--- a/ns-3.45/result_csv/cu_0119_1st_main_Load5.xlsx
+++ b/ns-3.45/result_csv/cu_0119_1st_main_Load5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE60DA6-8F46-4141-ABB3-8AF01723E158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE278D04-4838-E345-A12F-9C4BAB43A72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{D901B013-2279-A942-9DB6-FAF328F9E094}"/>
+    <workbookView xWindow="39300" yWindow="2000" windowWidth="38400" windowHeight="21000" xr2:uid="{D901B013-2279-A942-9DB6-FAF328F9E094}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1501,16 +1501,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>897466</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>694266</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>304797</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>220134</xdr:rowOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>101597</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>29634</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
